--- a/data_out/country_spreadsheets/Norway.xlsx
+++ b/data_out/country_spreadsheets/Norway.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>65.95</v>
       </c>
+      <c r="X2" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>113.02</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>148.11</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>7.39</v>
       </c>
+      <c r="X3" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>92.64</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>62.16</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>7.39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>6.94</v>
       </c>
+      <c r="X4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>48.92</v>
       </c>
+      <c r="X5" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>89.73999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>60.19</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>79.48</v>
       </c>
+      <c r="X6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>178.68</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>137.48</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>61.76</v>
       </c>
+      <c r="X7" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>137.05</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>61.76</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>60.22</v>
       </c>
+      <c r="X8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>132.76</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>154.41</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60.22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>73.48</v>
       </c>
+      <c r="X9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>104.68</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>73.48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>19.43</v>
       </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.43</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>10.39</v>
       </c>
+      <c r="X11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10.39</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>1.75</v>
       </c>
+      <c r="X12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1464,6 +2110,57 @@
         <v>2.08</v>
       </c>
       <c r="W13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2015</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN13" t="n">
         <v>1.91</v>
       </c>
     </row>
